--- a/outputs/84-40.xlsx
+++ b/outputs/84-40.xlsx
@@ -238,40 +238,44 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -527,222 +531,222 @@
   <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.27"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>44927</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="5" t="n">
         <v>2000</v>
       </c>
-      <c r="D2" s="4"/>
+      <c r="D2" s="5"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>44928</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="5" t="n">
         <v>2200</v>
       </c>
-      <c r="D3" s="4"/>
+      <c r="D3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>44929</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="5" t="n">
         <v>2400</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="5" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>44930</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="5" t="n">
         <v>2600</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="5" t="n">
         <v>1300</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>44931</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="5" t="n">
         <v>2800</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="5" t="n">
         <v>1400</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>44932</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4" t="n">
+      <c r="C7" s="5"/>
+      <c r="D7" s="5" t="n">
         <v>1500</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>44933</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4" t="n">
+      <c r="C8" s="5"/>
+      <c r="D8" s="5" t="n">
         <v>1600</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>44934</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4" t="n">
+      <c r="C9" s="5"/>
+      <c r="D9" s="5" t="n">
         <v>1700</v>
       </c>
-      <c r="E9" s="5"/>
+      <c r="E9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>44966</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4" t="n">
+      <c r="C10" s="5"/>
+      <c r="D10" s="5" t="n">
         <v>1800</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>44967</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="5" t="n">
         <v>3800</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>44968</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="5" t="n">
         <v>4000</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="5" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>44969</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="5" t="n">
         <v>4200</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="5" t="n">
         <v>2100</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>44970</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="5" t="n">
         <v>4400</v>
       </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>44971</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="5" t="n">
         <v>4400</v>
       </c>
-      <c r="D15" s="4"/>
+      <c r="D15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>44972</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="5" t="n">
         <v>4400</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="5" t="n">
         <v>2200</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -763,215 +767,215 @@
   <dimension ref="A1:D17"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.27"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>44927</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4" t="n">
+      <c r="C2" s="5"/>
+      <c r="D2" s="5" t="n">
         <v>400</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>44928</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="n">
+      <c r="C3" s="5"/>
+      <c r="D3" s="5" t="n">
         <v>500</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>44929</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="5" t="n">
         <v>400</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>44930</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="5" t="n">
         <v>6000</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="5" t="n">
         <v>1300</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>44931</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>44932</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4" t="n">
+      <c r="C7" s="5"/>
+      <c r="D7" s="5" t="n">
         <v>1500</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>44933</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4" t="n">
+      <c r="C8" s="5"/>
+      <c r="D8" s="5" t="n">
         <v>1600</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>44934</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4" t="n">
+      <c r="C9" s="5"/>
+      <c r="D9" s="5" t="n">
         <v>1700</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>44966</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4" t="n">
+      <c r="C10" s="5"/>
+      <c r="D10" s="5" t="n">
         <v>1800</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>44967</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>44968</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="5" t="n">
         <v>900</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="5" t="n">
         <v>600</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>44969</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="5" t="n">
         <v>6000</v>
       </c>
-      <c r="D13" s="4"/>
+      <c r="D13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>44970</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="5" t="n">
         <v>5000</v>
       </c>
-      <c r="D14" s="4"/>
+      <c r="D14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>44971</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="5" t="n">
         <v>2000</v>
       </c>
-      <c r="D15" s="4"/>
+      <c r="D15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>44972</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="5" t="n">
         <v>4400</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="5" t="n">
         <v>2200</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -992,91 +996,91 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>44927</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="5" t="n">
         <v>7000</v>
       </c>
-      <c r="D2" s="4"/>
+      <c r="D2" s="5"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>44928</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="5" t="n">
         <v>8000</v>
       </c>
-      <c r="D3" s="4"/>
+      <c r="D3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>44929</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="5" t="n">
         <v>5000</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="5" t="n">
         <v>400</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>44930</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="5" t="n">
         <v>6000</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>44931</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="5" t="n">
         <v>400</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1097,104 +1101,104 @@
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.36"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="n">
+      <c r="A2" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="8" t="n">
+      <c r="C2" s="9" t="n">
         <f aca="false">SUM(CA!C:C)</f>
         <v>37200</v>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="9" t="n">
         <f aca="false">SUM(CA!D:D)</f>
         <v>16800</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="9" t="n">
         <f aca="false">C2-D2</f>
         <v>20400</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="n">
+      <c r="A3" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="9" t="n">
         <f aca="false">SUM(MN!C:C)</f>
         <v>26300</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="9" t="n">
         <f aca="false">SUM(MN!D:D)</f>
         <v>12000</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="9" t="n">
         <f aca="false">C3-D3</f>
         <v>14300</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="n">
+      <c r="A4" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="8" t="n">
+      <c r="C4" s="9" t="n">
         <f aca="false">SUM(SDFRT!C:C)</f>
         <v>26500</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="9" t="n">
         <f aca="false">SUM(SDFRT!D:D)</f>
         <v>800</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="9" t="n">
         <f aca="false">C4-D4</f>
         <v>25700</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7" t="s">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="8" t="n">
-        <f aca="false">C2+C3+C4</f>
+      <c r="C5" s="9" t="n">
+        <f aca="false">SUM(C2:C4)</f>
         <v>90000</v>
       </c>
-      <c r="D5" s="8" t="n">
-        <f aca="false">D2+D3+D4</f>
+      <c r="D5" s="9" t="n">
+        <f aca="false">SUM(D2:D4)</f>
         <v>29600</v>
       </c>
-      <c r="E5" s="8" t="n">
-        <f aca="false">E2+E3+E4</f>
+      <c r="E5" s="9" t="n">
+        <f aca="false">SUM(E2:E4)</f>
         <v>60400</v>
       </c>
     </row>

--- a/outputs/84-40.xlsx
+++ b/outputs/84-40.xlsx
@@ -1125,18 +1125,16 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="n">
-        <v>1</v>
-      </c>
+      <c r="A2" s="8"/>
       <c r="B2" s="8" t="s">
         <v>32</v>
       </c>
       <c r="C2" s="9" t="n">
-        <f aca="false">SUM(CA!C:C)</f>
+        <f aca="false">SUM(CA!C2:C17)</f>
         <v>37200</v>
       </c>
       <c r="D2" s="9" t="n">
-        <f aca="false">SUM(CA!D:D)</f>
+        <f aca="false">SUM(CA!D2:D17)</f>
         <v>16800</v>
       </c>
       <c r="E2" s="9" t="n">
@@ -1145,18 +1143,16 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="n">
-        <v>2</v>
-      </c>
+      <c r="A3" s="8"/>
       <c r="B3" s="8" t="s">
         <v>33</v>
       </c>
       <c r="C3" s="9" t="n">
-        <f aca="false">SUM(MN!C:C)</f>
+        <f aca="false">SUM(MN!C2:C17)</f>
         <v>26300</v>
       </c>
       <c r="D3" s="9" t="n">
-        <f aca="false">SUM(MN!D:D)</f>
+        <f aca="false">SUM(MN!D2:D17)</f>
         <v>12000</v>
       </c>
       <c r="E3" s="9" t="n">
@@ -1165,18 +1161,16 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="n">
-        <v>3</v>
-      </c>
+      <c r="A4" s="8"/>
       <c r="B4" s="8" t="s">
         <v>34</v>
       </c>
       <c r="C4" s="9" t="n">
-        <f aca="false">SUM(SDFRT!C:C)</f>
+        <f aca="false">SUM(SDFRT!C2:C7)</f>
         <v>26500</v>
       </c>
       <c r="D4" s="9" t="n">
-        <f aca="false">SUM(SDFRT!D:D)</f>
+        <f aca="false">SUM(SDFRT!D2:D7)</f>
         <v>800</v>
       </c>
       <c r="E4" s="9" t="n">
@@ -1198,7 +1192,7 @@
         <v>29600</v>
       </c>
       <c r="E5" s="9" t="n">
-        <f aca="false">SUM(E2:E4)</f>
+        <f aca="false">C5-D5</f>
         <v>60400</v>
       </c>
     </row>
